--- a/mode_docx_gen/pmi_tokz/part/ltcblktoc/ptoc1/PTOC1.xlsx
+++ b/mode_docx_gen/pmi_tokz/part/ltcblktoc/ptoc1/PTOC1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\13. ТО блок РПН 35\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_tokz\part\ltcblktoc\ptoc1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="84">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>Токовый орган блокировки РПН</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Iset</t>
   </si>
 </sst>
 </file>
@@ -308,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -344,11 +350,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -359,6 +376,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -661,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -675,7 +695,7 @@
     <col min="28" max="28" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -766,8 +786,11 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="6" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -859,7 +882,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -951,7 +974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1043,7 +1066,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
@@ -1135,7 +1158,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -1227,7 +1250,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1319,7 +1342,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1409,6 +1432,9 @@
       </c>
       <c r="AD8" s="3" t="s">
         <v>32</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
